--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/116.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/116.xlsx
@@ -426,13 +426,13 @@
         <v>-17.20524431074119</v>
       </c>
       <c r="E2">
-        <v>-24.78972366286742</v>
+        <v>-10.95806802080204</v>
       </c>
       <c r="F2">
-        <v>-4.529527188001052</v>
+        <v>-0.5282707491978225</v>
       </c>
       <c r="G2">
-        <v>-16.45076714234525</v>
+        <v>-11.36565673069695</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-17.26991675094775</v>
       </c>
       <c r="E3">
-        <v>-25.75188567085647</v>
+        <v>-11.09254069707733</v>
       </c>
       <c r="F3">
-        <v>-4.520811106188796</v>
+        <v>-0.3946526020240538</v>
       </c>
       <c r="G3">
-        <v>-15.63125310982249</v>
+        <v>-11.11875208785389</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.29252346028013</v>
       </c>
       <c r="E4">
-        <v>-26.20157462705228</v>
+        <v>-12.14185369150659</v>
       </c>
       <c r="F4">
-        <v>-4.371850766347777</v>
+        <v>-0.2587017722440018</v>
       </c>
       <c r="G4">
-        <v>-15.22467402241464</v>
+        <v>-10.68748841033707</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-17.27128786094932</v>
       </c>
       <c r="E5">
-        <v>-26.1987504433514</v>
+        <v>-12.88054385774059</v>
       </c>
       <c r="F5">
-        <v>-4.26628693800462</v>
+        <v>-0.3145138543750212</v>
       </c>
       <c r="G5">
-        <v>-15.5975810314586</v>
+        <v>-10.64311227914962</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-17.19732414912749</v>
       </c>
       <c r="E6">
-        <v>-28.2788240372219</v>
+        <v>-14.26567306026151</v>
       </c>
       <c r="F6">
-        <v>-4.283738154079397</v>
+        <v>-0.2518859652537674</v>
       </c>
       <c r="G6">
-        <v>-15.02078661819936</v>
+        <v>-10.66356093615952</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-17.08382910318533</v>
       </c>
       <c r="E7">
-        <v>-26.1242958239312</v>
+        <v>-14.6002059260538</v>
       </c>
       <c r="F7">
-        <v>-3.635148843607259</v>
+        <v>0.02577864632761286</v>
       </c>
       <c r="G7">
-        <v>-15.70377959456362</v>
+        <v>-10.46654370633575</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.94397395914145</v>
       </c>
       <c r="E8">
-        <v>-28.91381266988626</v>
+        <v>-14.1145044744604</v>
       </c>
       <c r="F8">
-        <v>-4.277699355712988</v>
+        <v>0.3498401161397934</v>
       </c>
       <c r="G8">
-        <v>-14.44337998533349</v>
+        <v>-9.691583335632632</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.7857531098144</v>
       </c>
       <c r="E9">
-        <v>-28.9855967744246</v>
+        <v>-15.33260813034201</v>
       </c>
       <c r="F9">
-        <v>-3.463369466921323</v>
+        <v>0.3392709764474746</v>
       </c>
       <c r="G9">
-        <v>-15.23025971046733</v>
+        <v>-9.259522075643225</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.63753863034922</v>
       </c>
       <c r="E10">
-        <v>-29.17889138269345</v>
+        <v>-16.02155113132723</v>
       </c>
       <c r="F10">
-        <v>-4.277233813232615</v>
+        <v>0.3451383027615035</v>
       </c>
       <c r="G10">
-        <v>-14.43635186089421</v>
+        <v>-8.867072337962485</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-16.49620395772879</v>
       </c>
       <c r="E11">
-        <v>-28.91304017257984</v>
+        <v>-16.79946422531291</v>
       </c>
       <c r="F11">
-        <v>-3.590003648522089</v>
+        <v>0.6619333337163268</v>
       </c>
       <c r="G11">
-        <v>-13.78082652837306</v>
+        <v>-8.314997759864193</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-16.39780488903904</v>
       </c>
       <c r="E12">
-        <v>-29.47107810581778</v>
+        <v>-17.72666450036956</v>
       </c>
       <c r="F12">
-        <v>-3.641002916042844</v>
+        <v>1.152009571458362</v>
       </c>
       <c r="G12">
-        <v>-14.8135692092581</v>
+        <v>-7.670616390630203</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-16.32635746245595</v>
       </c>
       <c r="E13">
-        <v>-29.42076195061749</v>
+        <v>-18.51680880170686</v>
       </c>
       <c r="F13">
-        <v>-3.231219502286762</v>
+        <v>1.24911079841452</v>
       </c>
       <c r="G13">
-        <v>-13.34010673394722</v>
+        <v>-7.067735417416549</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-16.29879074746843</v>
       </c>
       <c r="E14">
-        <v>-31.43919981182187</v>
+        <v>-19.72423870448366</v>
       </c>
       <c r="F14">
-        <v>-3.324773660024132</v>
+        <v>1.185041550012395</v>
       </c>
       <c r="G14">
-        <v>-13.60673816292074</v>
+        <v>-7.269159584110121</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-16.28611858519472</v>
       </c>
       <c r="E15">
-        <v>-33.19687414678557</v>
+        <v>-20.44353337383072</v>
       </c>
       <c r="F15">
-        <v>-2.589053352655932</v>
+        <v>1.22269913214366</v>
       </c>
       <c r="G15">
-        <v>-13.82238175002981</v>
+        <v>-6.948105878762556</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-16.27269921649485</v>
       </c>
       <c r="E16">
-        <v>-32.79005256127898</v>
+        <v>-21.49103556812235</v>
       </c>
       <c r="F16">
-        <v>-2.626336512721132</v>
+        <v>1.806711404995757</v>
       </c>
       <c r="G16">
-        <v>-12.92008231189514</v>
+        <v>-6.393630721012734</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-16.22992967183152</v>
       </c>
       <c r="E17">
-        <v>-33.33657986933015</v>
+        <v>-22.41158239863662</v>
       </c>
       <c r="F17">
-        <v>-2.717515741114676</v>
+        <v>2.154687013359356</v>
       </c>
       <c r="G17">
-        <v>-13.96641391837693</v>
+        <v>-6.305969749876923</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-16.12790697610685</v>
       </c>
       <c r="E18">
-        <v>-33.92868451846</v>
+        <v>-22.36844299260563</v>
       </c>
       <c r="F18">
-        <v>-2.519251801826434</v>
+        <v>2.516396953261371</v>
       </c>
       <c r="G18">
-        <v>-13.01785208608774</v>
+        <v>-6.782302711270133</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-15.95658253639828</v>
       </c>
       <c r="E19">
-        <v>-34.40560815791837</v>
+        <v>-23.89668770416881</v>
       </c>
       <c r="F19">
-        <v>-2.646994339012146</v>
+        <v>2.885439601412968</v>
       </c>
       <c r="G19">
-        <v>-12.87082017220543</v>
+        <v>-5.565249294486262</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-15.69011116215289</v>
       </c>
       <c r="E20">
-        <v>-34.56457232137618</v>
+        <v>-24.9409711596837</v>
       </c>
       <c r="F20">
-        <v>-1.543140930900623</v>
+        <v>3.122342738204793</v>
       </c>
       <c r="G20">
-        <v>-13.16139473982404</v>
+        <v>-5.640937390927228</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-15.34424189943372</v>
       </c>
       <c r="E21">
-        <v>-35.33250940175963</v>
+        <v>-25.40133386898432</v>
       </c>
       <c r="F21">
-        <v>-1.144991108949457</v>
+        <v>3.738571876086568</v>
       </c>
       <c r="G21">
-        <v>-12.82906392321516</v>
+        <v>-5.695880510847206</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-14.90498719972623</v>
       </c>
       <c r="E22">
-        <v>-35.70267474411328</v>
+        <v>-26.01637462765553</v>
       </c>
       <c r="F22">
-        <v>-1.682140152722977</v>
+        <v>3.908146967113654</v>
       </c>
       <c r="G22">
-        <v>-12.46875506219562</v>
+        <v>-6.307400437912854</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-14.40366864320624</v>
       </c>
       <c r="E23">
-        <v>-37.35087250516017</v>
+        <v>-26.01026940700803</v>
       </c>
       <c r="F23">
-        <v>-1.618642477828784</v>
+        <v>4.037069099480953</v>
       </c>
       <c r="G23">
-        <v>-12.59129427569641</v>
+        <v>-5.950412444013205</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-13.84903111182956</v>
       </c>
       <c r="E24">
-        <v>-35.18864008486191</v>
+        <v>-26.03859430824336</v>
       </c>
       <c r="F24">
-        <v>-1.172290785076118</v>
+        <v>3.671702745862981</v>
       </c>
       <c r="G24">
-        <v>-11.49168259359917</v>
+        <v>-6.051967797862921</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-13.2759858980701</v>
       </c>
       <c r="E25">
-        <v>-37.98065301082319</v>
+        <v>-25.67023353621034</v>
       </c>
       <c r="F25">
-        <v>-1.304371482350291</v>
+        <v>4.35651076428772</v>
       </c>
       <c r="G25">
-        <v>-12.74375262221135</v>
+        <v>-5.699284921794018</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-12.71126548588162</v>
       </c>
       <c r="E26">
-        <v>-37.12992373928495</v>
+        <v>-26.51262108280267</v>
       </c>
       <c r="F26">
-        <v>-1.017227862578675</v>
+        <v>3.927320359018852</v>
       </c>
       <c r="G26">
-        <v>-12.88706291967904</v>
+        <v>-5.854125572748356</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-12.17869188506114</v>
       </c>
       <c r="E27">
-        <v>-37.60391728815366</v>
+        <v>-26.39816688511304</v>
       </c>
       <c r="F27">
-        <v>-1.757318636364046</v>
+        <v>4.066237572468329</v>
       </c>
       <c r="G27">
-        <v>-12.70460059095072</v>
+        <v>-6.090484112815615</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-11.70983390043683</v>
       </c>
       <c r="E28">
-        <v>-37.75950696741005</v>
+        <v>-25.69329216548579</v>
       </c>
       <c r="F28">
-        <v>-1.344241633814433</v>
+        <v>3.737925749512384</v>
       </c>
       <c r="G28">
-        <v>-12.09990123412936</v>
+        <v>-5.992040766518507</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-11.30957557242312</v>
       </c>
       <c r="E29">
-        <v>-36.12083044332533</v>
+        <v>-26.60117585467066</v>
       </c>
       <c r="F29">
-        <v>-1.559640352829583</v>
+        <v>3.73907552346747</v>
       </c>
       <c r="G29">
-        <v>-11.55413943645238</v>
+        <v>-6.243424141707623</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-11.00751894472251</v>
       </c>
       <c r="E30">
-        <v>-35.6977178863971</v>
+        <v>-26.92157534232456</v>
       </c>
       <c r="F30">
-        <v>-1.507376168284754</v>
+        <v>3.411076823389783</v>
       </c>
       <c r="G30">
-        <v>-13.01331722273298</v>
+        <v>-5.607438927078653</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.79002019871616</v>
       </c>
       <c r="E31">
-        <v>-35.40101039274569</v>
+        <v>-26.63138631384746</v>
       </c>
       <c r="F31">
-        <v>-1.519137328669701</v>
+        <v>3.415072867740888</v>
       </c>
       <c r="G31">
-        <v>-11.72483644468084</v>
+        <v>-6.063838853518713</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.67387570166177</v>
       </c>
       <c r="E32">
-        <v>-36.03878583020901</v>
+        <v>-24.7085076154104</v>
       </c>
       <c r="F32">
-        <v>-1.85929811895529</v>
+        <v>3.323137339908588</v>
       </c>
       <c r="G32">
-        <v>-12.89189540791719</v>
+        <v>-6.813819619974053</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.63821666004188</v>
       </c>
       <c r="E33">
-        <v>-36.42684320695002</v>
+        <v>-25.16845085036721</v>
       </c>
       <c r="F33">
-        <v>-1.069319746703722</v>
+        <v>3.622355242943408</v>
       </c>
       <c r="G33">
-        <v>-13.10037772261284</v>
+        <v>-6.392938873696089</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.67956133022206</v>
       </c>
       <c r="E34">
-        <v>-35.12161348389616</v>
+        <v>-25.13852696277182</v>
       </c>
       <c r="F34">
-        <v>-0.5749036921384206</v>
+        <v>3.612146443071307</v>
       </c>
       <c r="G34">
-        <v>-12.9861380661672</v>
+        <v>-6.641236348778509</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.78007042489965</v>
       </c>
       <c r="E35">
-        <v>-35.03761063164018</v>
+        <v>-24.3331071501818</v>
       </c>
       <c r="F35">
-        <v>-1.695355097899838</v>
+        <v>3.581473654880447</v>
       </c>
       <c r="G35">
-        <v>-13.3414643211346</v>
+        <v>-7.070233899990244</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-10.92276920359446</v>
       </c>
       <c r="E36">
-        <v>-33.61483049185403</v>
+        <v>-23.2691167069306</v>
       </c>
       <c r="F36">
-        <v>-1.578339918580379</v>
+        <v>3.492955970952098</v>
       </c>
       <c r="G36">
-        <v>-12.61172465749416</v>
+        <v>-7.337772562709169</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.10005690342988</v>
       </c>
       <c r="E37">
-        <v>-35.35128399355352</v>
+        <v>-23.2563538885294</v>
       </c>
       <c r="F37">
-        <v>-1.196870102651985</v>
+        <v>3.601949240342845</v>
       </c>
       <c r="G37">
-        <v>-13.34251384046023</v>
+        <v>-7.637841103033366</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.28791248074362</v>
       </c>
       <c r="E38">
-        <v>-33.95080244537037</v>
+        <v>-22.37948638151835</v>
       </c>
       <c r="F38">
-        <v>-1.441359428118647</v>
+        <v>3.771484569734598</v>
       </c>
       <c r="G38">
-        <v>-13.3156127281934</v>
+        <v>-7.80974558063522</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-11.49316863624423</v>
       </c>
       <c r="E39">
-        <v>-33.07489433017535</v>
+        <v>-21.80008017601417</v>
       </c>
       <c r="F39">
-        <v>-1.42035451588586</v>
+        <v>3.521272882249396</v>
       </c>
       <c r="G39">
-        <v>-13.41148057495137</v>
+        <v>-7.535907191217939</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-11.69423465322438</v>
       </c>
       <c r="E40">
-        <v>-31.38025536009424</v>
+        <v>-22.19605565014597</v>
       </c>
       <c r="F40">
-        <v>-1.6701039743603</v>
+        <v>3.780291771961162</v>
       </c>
       <c r="G40">
-        <v>-13.49668875154383</v>
+        <v>-8.268837184748719</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-11.90571288617681</v>
       </c>
       <c r="E41">
-        <v>-32.58369817999921</v>
+        <v>-21.82264457314196</v>
       </c>
       <c r="F41">
-        <v>-1.564544287854156</v>
+        <v>4.153313897115807</v>
       </c>
       <c r="G41">
-        <v>-13.83535715064764</v>
+        <v>-8.40255691196095</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-12.11341408377283</v>
       </c>
       <c r="E42">
-        <v>-31.72895067650419</v>
+        <v>-20.79561355747041</v>
       </c>
       <c r="F42">
-        <v>-0.8955713407013317</v>
+        <v>3.966932888220724</v>
       </c>
       <c r="G42">
-        <v>-12.58389673089749</v>
+        <v>-8.437320281563919</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-12.326321209379</v>
       </c>
       <c r="E43">
-        <v>-33.0155532467662</v>
+        <v>-19.88993937671035</v>
       </c>
       <c r="F43">
-        <v>-1.520925773892346</v>
+        <v>3.940874106463458</v>
       </c>
       <c r="G43">
-        <v>-14.75728677736288</v>
+        <v>-8.732547196043896</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-12.54219955806633</v>
       </c>
       <c r="E44">
-        <v>-32.37737702441004</v>
+        <v>-19.73340484187756</v>
       </c>
       <c r="F44">
-        <v>-1.166171635071638</v>
+        <v>3.956188963006415</v>
       </c>
       <c r="G44">
-        <v>-14.01578701471177</v>
+        <v>-8.930606112959524</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-12.76401832974849</v>
       </c>
       <c r="E45">
-        <v>-31.58429432606042</v>
+        <v>-18.35451791597786</v>
       </c>
       <c r="F45">
-        <v>-1.784310988184268</v>
+        <v>3.854690761876197</v>
       </c>
       <c r="G45">
-        <v>-13.87691628842128</v>
+        <v>-8.898709340917597</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-13.0026056982598</v>
       </c>
       <c r="E46">
-        <v>-31.37801677919016</v>
+        <v>-18.86727338614119</v>
       </c>
       <c r="F46">
-        <v>-1.05389388892879</v>
+        <v>3.847280187090753</v>
       </c>
       <c r="G46">
-        <v>-13.99892682614236</v>
+        <v>-8.697993991380512</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-13.25086084388252</v>
       </c>
       <c r="E47">
-        <v>-30.62051048904902</v>
+        <v>-17.19952230617702</v>
       </c>
       <c r="F47">
-        <v>-1.520953938384041</v>
+        <v>4.004635202191741</v>
       </c>
       <c r="G47">
-        <v>-14.43367584768832</v>
+        <v>-8.799352234013599</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-13.52700307773958</v>
       </c>
       <c r="E48">
-        <v>-29.89767105383622</v>
+        <v>-17.21579043493637</v>
       </c>
       <c r="F48">
-        <v>-1.056171899286489</v>
+        <v>3.822709153188914</v>
       </c>
       <c r="G48">
-        <v>-12.45149804044836</v>
+        <v>-8.530786243298071</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-13.81243306189342</v>
       </c>
       <c r="E49">
-        <v>-28.7381214478177</v>
+        <v>-16.35691463938448</v>
       </c>
       <c r="F49">
-        <v>-1.632327935690434</v>
+        <v>3.748653107378638</v>
       </c>
       <c r="G49">
-        <v>-12.85357098269194</v>
+        <v>-8.985772451542042</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-14.12225217400564</v>
       </c>
       <c r="E50">
-        <v>-28.6821756146666</v>
+        <v>-16.40873841029569</v>
       </c>
       <c r="F50">
-        <v>-1.812192178227694</v>
+        <v>3.604363102954603</v>
       </c>
       <c r="G50">
-        <v>-13.29163303912402</v>
+        <v>-9.293161519699721</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-14.43481479010089</v>
       </c>
       <c r="E51">
-        <v>-27.73648524279182</v>
+        <v>-15.31940922475171</v>
       </c>
       <c r="F51">
-        <v>-1.896996291089293</v>
+        <v>4.081373501652282</v>
       </c>
       <c r="G51">
-        <v>-13.67836916226711</v>
+        <v>-8.674616078939387</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-14.75305792009669</v>
       </c>
       <c r="E52">
-        <v>-28.95347376143271</v>
+        <v>-14.71417835122975</v>
       </c>
       <c r="F52">
-        <v>-1.870730417481326</v>
+        <v>3.929242171393347</v>
       </c>
       <c r="G52">
-        <v>-14.08331392356092</v>
+        <v>-8.997939826708926</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-15.06262355018629</v>
       </c>
       <c r="E53">
-        <v>-29.31409502416192</v>
+        <v>-14.60327099601153</v>
       </c>
       <c r="F53">
-        <v>-1.527937075589641</v>
+        <v>3.647961736098747</v>
       </c>
       <c r="G53">
-        <v>-13.25139754885808</v>
+        <v>-9.141029516258662</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-15.35513691562004</v>
       </c>
       <c r="E54">
-        <v>-28.91696495728181</v>
+        <v>-14.69681792789196</v>
       </c>
       <c r="F54">
-        <v>-2.279079098895759</v>
+        <v>3.760719106967815</v>
       </c>
       <c r="G54">
-        <v>-12.71999093031534</v>
+        <v>-8.93510442589001</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-15.62900165044662</v>
       </c>
       <c r="E55">
-        <v>-27.6091187110933</v>
+        <v>-15.20461031052212</v>
       </c>
       <c r="F55">
-        <v>-1.786231143823957</v>
+        <v>3.606427394522379</v>
       </c>
       <c r="G55">
-        <v>-13.46683358177216</v>
+        <v>-9.19294417245295</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-15.86778118405816</v>
       </c>
       <c r="E56">
-        <v>-25.56286056382955</v>
+        <v>-13.38364726478503</v>
       </c>
       <c r="F56">
-        <v>-1.69417218924864</v>
+        <v>3.70307964634622</v>
       </c>
       <c r="G56">
-        <v>-14.11935916875813</v>
+        <v>-9.112648111808671</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-16.08518317340153</v>
       </c>
       <c r="E57">
-        <v>-27.37926338353199</v>
+        <v>-13.20457740530372</v>
       </c>
       <c r="F57">
-        <v>-1.951399320268151</v>
+        <v>3.454248018954082</v>
       </c>
       <c r="G57">
-        <v>-13.88890091146678</v>
+        <v>-9.10733394119346</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-16.26030662066837</v>
       </c>
       <c r="E58">
-        <v>-27.03931888338345</v>
+        <v>-12.81227336998306</v>
       </c>
       <c r="F58">
-        <v>-2.067906710369693</v>
+        <v>3.621884730258618</v>
       </c>
       <c r="G58">
-        <v>-13.70105392201929</v>
+        <v>-9.998820980604027</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-16.41328062446695</v>
       </c>
       <c r="E59">
-        <v>-25.4358719743616</v>
+        <v>-12.37851197921797</v>
       </c>
       <c r="F59">
-        <v>-1.843080341943282</v>
+        <v>3.489279676418473</v>
       </c>
       <c r="G59">
-        <v>-14.02824940401745</v>
+        <v>-10.03538445860257</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-16.52698236968575</v>
       </c>
       <c r="E60">
-        <v>-25.0882232672055</v>
+        <v>-12.32144685561483</v>
       </c>
       <c r="F60">
-        <v>-2.082823122191904</v>
+        <v>3.929175902001123</v>
       </c>
       <c r="G60">
-        <v>-14.29606219491844</v>
+        <v>-9.523812972090806</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-16.61437233386532</v>
       </c>
       <c r="E61">
-        <v>-25.78262358787153</v>
+        <v>-12.2614412583937</v>
       </c>
       <c r="F61">
-        <v>-1.26548460299327</v>
+        <v>3.75134364470293</v>
       </c>
       <c r="G61">
-        <v>-14.83166297464681</v>
+        <v>-9.486786086927342</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-16.66937612999883</v>
       </c>
       <c r="E62">
-        <v>-26.04460400503039</v>
+        <v>-11.55718952046518</v>
       </c>
       <c r="F62">
-        <v>-1.64777533101784</v>
+        <v>3.680448648901738</v>
       </c>
       <c r="G62">
-        <v>-13.33011802514162</v>
+        <v>-10.30986509118926</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-16.69374218407712</v>
       </c>
       <c r="E63">
-        <v>-26.52295427257884</v>
+        <v>-11.00926050359187</v>
       </c>
       <c r="F63">
-        <v>-1.855319470319645</v>
+        <v>4.053278592818933</v>
       </c>
       <c r="G63">
-        <v>-14.0022359449116</v>
+        <v>-10.3528040074793</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-16.69178216238758</v>
       </c>
       <c r="E64">
-        <v>-26.18668536445277</v>
+        <v>-11.19222607529587</v>
       </c>
       <c r="F64">
-        <v>-1.694458804370008</v>
+        <v>3.391376589816405</v>
       </c>
       <c r="G64">
-        <v>-14.64776473639339</v>
+        <v>-10.11111432695699</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-16.65115665959379</v>
       </c>
       <c r="E65">
-        <v>-26.74576575373324</v>
+        <v>-10.76429164001951</v>
       </c>
       <c r="F65">
-        <v>-1.512661152314615</v>
+        <v>3.537439300482431</v>
       </c>
       <c r="G65">
-        <v>-14.78240475107398</v>
+        <v>-10.73128887234218</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-16.58600560348147</v>
       </c>
       <c r="E66">
-        <v>-25.78789401304274</v>
+        <v>-11.13540183794957</v>
       </c>
       <c r="F66">
-        <v>-1.724202164334927</v>
+        <v>3.324673133073378</v>
       </c>
       <c r="G66">
-        <v>-14.61234476452575</v>
+        <v>-10.69406748670668</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-16.47570210638692</v>
       </c>
       <c r="E67">
-        <v>-23.22120110787605</v>
+        <v>-10.57998042784627</v>
       </c>
       <c r="F67">
-        <v>-1.522375416847245</v>
+        <v>3.493731322841118</v>
       </c>
       <c r="G67">
-        <v>-14.62753407655685</v>
+        <v>-10.2822381919261</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-16.3411107876339</v>
       </c>
       <c r="E68">
-        <v>-26.58840057663549</v>
+        <v>-11.32218005764975</v>
       </c>
       <c r="F68">
-        <v>-2.175350104349802</v>
+        <v>3.54605266473674</v>
       </c>
       <c r="G68">
-        <v>-14.48858633330091</v>
+        <v>-10.43723026606672</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-16.16532463100629</v>
       </c>
       <c r="E69">
-        <v>-26.36407317334752</v>
+        <v>-10.80403787239812</v>
       </c>
       <c r="F69">
-        <v>-2.67175341231442</v>
+        <v>3.595280882750309</v>
       </c>
       <c r="G69">
-        <v>-14.73579643326113</v>
+        <v>-10.50258373004377</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-15.96505369813957</v>
       </c>
       <c r="E70">
-        <v>-24.90888344898807</v>
+        <v>-11.10653286603068</v>
       </c>
       <c r="F70">
-        <v>-2.19408280479671</v>
+        <v>3.649399781910007</v>
       </c>
       <c r="G70">
-        <v>-14.39545454687442</v>
+        <v>-10.26396167441601</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-15.73655516742884</v>
       </c>
       <c r="E71">
-        <v>-24.72451824506761</v>
+        <v>-10.92418196960276</v>
       </c>
       <c r="F71">
-        <v>-1.676632337861763</v>
+        <v>3.345547991623925</v>
       </c>
       <c r="G71">
-        <v>-15.47997873597961</v>
+        <v>-10.21147787590086</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-15.4879706115391</v>
       </c>
       <c r="E72">
-        <v>-24.80936419922254</v>
+        <v>-11.03738189747229</v>
       </c>
       <c r="F72">
-        <v>-2.209029866212825</v>
+        <v>3.523032334612942</v>
       </c>
       <c r="G72">
-        <v>-14.11567279739547</v>
+        <v>-10.31444564257437</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-15.23110882172909</v>
       </c>
       <c r="E73">
-        <v>-25.40260475164972</v>
+        <v>-11.55923705364832</v>
       </c>
       <c r="F73">
-        <v>-2.216934976337741</v>
+        <v>3.644104857471312</v>
       </c>
       <c r="G73">
-        <v>-14.53509022133012</v>
+        <v>-10.32857760304607</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-14.96478980960844</v>
       </c>
       <c r="E74">
-        <v>-26.28060608535245</v>
+        <v>-11.24681173173809</v>
       </c>
       <c r="F74">
-        <v>-2.020501729009685</v>
+        <v>3.456390177057722</v>
       </c>
       <c r="G74">
-        <v>-13.8098110148236</v>
+        <v>-10.29635187718566</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-14.7120444448927</v>
       </c>
       <c r="E75">
-        <v>-24.94455538105703</v>
+        <v>-12.03735058815126</v>
       </c>
       <c r="F75">
-        <v>-2.514916126840181</v>
+        <v>3.486799544414492</v>
       </c>
       <c r="G75">
-        <v>-13.79401339930277</v>
+        <v>-9.93624143275504</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-14.46090693725314</v>
       </c>
       <c r="E76">
-        <v>-25.69661888775698</v>
+        <v>-11.96188673837912</v>
       </c>
       <c r="F76">
-        <v>-1.931646071180994</v>
+        <v>3.582292081874413</v>
       </c>
       <c r="G76">
-        <v>-14.35719277951936</v>
+        <v>-10.03250611269086</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-14.23787197672855</v>
       </c>
       <c r="E77">
-        <v>-25.88995502813907</v>
+        <v>-11.84091199890952</v>
       </c>
       <c r="F77">
-        <v>-2.030137298639049</v>
+        <v>3.145956179388996</v>
       </c>
       <c r="G77">
-        <v>-15.37534400888468</v>
+        <v>-10.51769863585402</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-14.02881960061978</v>
       </c>
       <c r="E78">
-        <v>-25.47803952894258</v>
+        <v>-12.90999843245628</v>
       </c>
       <c r="F78">
-        <v>-2.686733608426647</v>
+        <v>3.477675905840058</v>
       </c>
       <c r="G78">
-        <v>-14.5961150707751</v>
+        <v>-9.863636625676181</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-13.850373553285</v>
       </c>
       <c r="E79">
-        <v>-26.1649599160126</v>
+        <v>-12.39457660062241</v>
       </c>
       <c r="F79">
-        <v>-2.324654216662983</v>
+        <v>3.308549789945288</v>
       </c>
       <c r="G79">
-        <v>-14.9724473767226</v>
+        <v>-10.20186903043327</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-13.69328996701415</v>
       </c>
       <c r="E80">
-        <v>-25.54981117384694</v>
+        <v>-12.8767810482803</v>
       </c>
       <c r="F80">
-        <v>-2.056470270006643</v>
+        <v>3.697044161449423</v>
       </c>
       <c r="G80">
-        <v>-14.17974046966139</v>
+        <v>-9.728418331068649</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-13.55847654996802</v>
       </c>
       <c r="E81">
-        <v>-25.87954708055905</v>
+        <v>-13.80232419201834</v>
       </c>
       <c r="F81">
-        <v>-2.591002501154719</v>
+        <v>3.452407386585062</v>
       </c>
       <c r="G81">
-        <v>-14.02468834839518</v>
+        <v>-9.412405973526525</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-13.44467473838378</v>
       </c>
       <c r="E82">
-        <v>-27.21118292121618</v>
+        <v>-14.84907465506018</v>
       </c>
       <c r="F82">
-        <v>-2.278935791335075</v>
+        <v>3.436761183080985</v>
       </c>
       <c r="G82">
-        <v>-14.04426893282852</v>
+        <v>-9.071992291663559</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-13.33950048615251</v>
       </c>
       <c r="E83">
-        <v>-27.6279036859155</v>
+        <v>-15.70851528735225</v>
       </c>
       <c r="F83">
-        <v>-2.208428471478392</v>
+        <v>3.36790728456029</v>
       </c>
       <c r="G83">
-        <v>-14.04421410719211</v>
+        <v>-8.558402699582865</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-13.2517322849212</v>
       </c>
       <c r="E84">
-        <v>-28.25083139289256</v>
+        <v>-16.05636750186326</v>
       </c>
       <c r="F84">
-        <v>-2.201141323435965</v>
+        <v>3.137245067781156</v>
       </c>
       <c r="G84">
-        <v>-14.34557496608891</v>
+        <v>-8.706643388210869</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-13.1600086636781</v>
       </c>
       <c r="E85">
-        <v>-28.31821309342658</v>
+        <v>-17.62231921904456</v>
       </c>
       <c r="F85">
-        <v>-1.820102258557026</v>
+        <v>3.123444466850517</v>
       </c>
       <c r="G85">
-        <v>-13.54830708822703</v>
+        <v>-8.870273110831191</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-13.07839758085953</v>
       </c>
       <c r="E86">
-        <v>-28.46482768301001</v>
+        <v>-17.49582901493559</v>
       </c>
       <c r="F86">
-        <v>-2.556589634140219</v>
+        <v>3.08816264243048</v>
       </c>
       <c r="G86">
-        <v>-14.13846981916507</v>
+        <v>-8.656428326745397</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-12.98482273884352</v>
       </c>
       <c r="E87">
-        <v>-31.3744616302961</v>
+        <v>-19.88677878289215</v>
       </c>
       <c r="F87">
-        <v>-1.783026190342526</v>
+        <v>2.944028371078172</v>
       </c>
       <c r="G87">
-        <v>-14.82595197085375</v>
+        <v>-8.313248560988146</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-12.88948353368935</v>
       </c>
       <c r="E88">
-        <v>-30.75241440411991</v>
+        <v>-20.45035294682609</v>
       </c>
       <c r="F88">
-        <v>-2.472448215200859</v>
+        <v>3.150230555187441</v>
       </c>
       <c r="G88">
-        <v>-13.60761145698646</v>
+        <v>-8.185205897889292</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-12.78131272074405</v>
       </c>
       <c r="E89">
-        <v>-32.42541514319867</v>
+        <v>-22.06359728136322</v>
       </c>
       <c r="F89">
-        <v>-2.242124800689471</v>
+        <v>2.907822088636611</v>
       </c>
       <c r="G89">
-        <v>-12.90512535613266</v>
+        <v>-7.826420406338661</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-12.66311847845097</v>
       </c>
       <c r="E90">
-        <v>-34.39970436802012</v>
+        <v>-24.07290015425864</v>
       </c>
       <c r="F90">
-        <v>-2.376737817114002</v>
+        <v>2.764806113278082</v>
       </c>
       <c r="G90">
-        <v>-13.54084296944104</v>
+        <v>-8.300586449721248</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-12.53646835400586</v>
       </c>
       <c r="E91">
-        <v>-35.31146507997672</v>
+        <v>-25.52136582948319</v>
       </c>
       <c r="F91">
-        <v>-2.502033356991844</v>
+        <v>2.793177696823965</v>
       </c>
       <c r="G91">
-        <v>-14.35219711974427</v>
+        <v>-7.614584590215729</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-12.39730507274044</v>
       </c>
       <c r="E92">
-        <v>-37.22471455795718</v>
+        <v>-27.30583460730902</v>
       </c>
       <c r="F92">
-        <v>-2.709883992232685</v>
+        <v>2.853565680488049</v>
       </c>
       <c r="G92">
-        <v>-12.98449460244709</v>
+        <v>-7.941216151382208</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-12.25983007341481</v>
       </c>
       <c r="E93">
-        <v>-36.53130477819212</v>
+        <v>-29.10988577653142</v>
       </c>
       <c r="F93">
-        <v>-2.396645142538079</v>
+        <v>2.477765211064414</v>
       </c>
       <c r="G93">
-        <v>-14.9672454681248</v>
+        <v>-7.932317428443398</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-12.11223804076274</v>
       </c>
       <c r="E94">
-        <v>-38.62954036518609</v>
+        <v>-31.26202589331035</v>
       </c>
       <c r="F94">
-        <v>-2.593711262561873</v>
+        <v>2.432688770473676</v>
       </c>
       <c r="G94">
-        <v>-14.16192866468852</v>
+        <v>-8.230480125216083</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-11.97547871309482</v>
       </c>
       <c r="E95">
-        <v>-39.87565327824235</v>
+        <v>-33.87637274521812</v>
       </c>
       <c r="F95">
-        <v>-2.758488449591945</v>
+        <v>2.257020208831596</v>
       </c>
       <c r="G95">
-        <v>-14.04049901763896</v>
+        <v>-7.79044434587312</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-11.83749016035925</v>
       </c>
       <c r="E96">
-        <v>-42.18354297291367</v>
+        <v>-35.81329137453877</v>
       </c>
       <c r="F96">
-        <v>-2.211920040081192</v>
+        <v>1.696778766970234</v>
       </c>
       <c r="G96">
-        <v>-14.95153531254778</v>
+        <v>-8.786656183067015</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-11.71577571439645</v>
       </c>
       <c r="E97">
-        <v>-44.82219441749434</v>
+        <v>-37.79143893268099</v>
       </c>
       <c r="F97">
-        <v>-3.622936222987786</v>
+        <v>1.580969690589252</v>
       </c>
       <c r="G97">
-        <v>-13.86595377188319</v>
+        <v>-8.578173868371367</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-11.60800211600031</v>
       </c>
       <c r="E98">
-        <v>-45.30863098749223</v>
+        <v>-40.88536955590069</v>
       </c>
       <c r="F98">
-        <v>-2.558406243854559</v>
+        <v>1.347239200950149</v>
       </c>
       <c r="G98">
-        <v>-14.763099600195</v>
+        <v>-9.011937333834179</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.52009271525158</v>
       </c>
       <c r="E99">
-        <v>-48.21173712487852</v>
+        <v>-42.73224864030472</v>
       </c>
       <c r="F99">
-        <v>-3.214037505617894</v>
+        <v>0.9990846652275451</v>
       </c>
       <c r="G99">
-        <v>-15.59648190798575</v>
+        <v>-9.24571906899001</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.46005096939762</v>
       </c>
       <c r="E100">
-        <v>-48.65763939064892</v>
+        <v>-45.34237582950647</v>
       </c>
       <c r="F100">
-        <v>-3.25849184228913</v>
+        <v>0.8640011361182242</v>
       </c>
       <c r="G100">
-        <v>-14.4804525585273</v>
+        <v>-9.747997610129703</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.41779872528602</v>
       </c>
       <c r="E101">
-        <v>-50.06631833968445</v>
+        <v>-48.51092616229652</v>
       </c>
       <c r="F101">
-        <v>-2.759412907613469</v>
+        <v>0.5913266097713081</v>
       </c>
       <c r="G101">
-        <v>-14.57953162113234</v>
+        <v>-8.973383163084915</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.41553202780843</v>
       </c>
       <c r="E102">
-        <v>-52.76932690865183</v>
+        <v>-50.60953034679558</v>
       </c>
       <c r="F102">
-        <v>-4.233232593530711</v>
+        <v>0.152280289143931</v>
       </c>
       <c r="G102">
-        <v>-14.68974942553537</v>
+        <v>-9.803351922322783</v>
       </c>
     </row>
   </sheetData>
